--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0120.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0120.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Thịt tươi à? Cậu từ đâu tới vậy?</t>
+          <t>Thịt tươi à? Mày từ đâu tới vậy?</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Haha! Tất nhiên là ta làm được rồi! Nếu ai cũng có thể lẻn vào đây dễ dàng thế, thì chúng ta còn mặt mũi nào mà xưng danh Icebreakers nữa chứ?</t>
+          <t>Haha! Tất nhiên là tao làm được rồi! Nếu ai cũng có thể lẻn vào đây dễ dàng thế, thì chúng tao còn mặt mũi nào mà xưng danh Icebreakers nữa chứ?</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Vậy đây là câu trả lời của cậu hả? Ha! Thế thì ta sẽ tự giải quyết vậy.</t>
+          <t>Vậy đây là câu trả lời của cậu hả? Ha! Thế thì tao sẽ tự giải quyết vậy.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đồ ngốc! Toàn đồ ngốc! R?i ?i! Ta chỉ cần ngai vàng của ta thôi... Haha!</t>
+          <t>Đồ ngốc! Toàn đồ ngốc! Cút đi! Ta chỉ cần ngai vàng của ta thôi... Haha!</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Không phải chuyện cá nhân đâu. Không ai được phép lại gần để tránh cản trở hoạt động săn lùng của chúng tôi. Vậy nên ta sẽ phải yêu cầu cậu...</t>
+          <t>Không phải chuyện cá nhân đâu. Không ai được phép lại gần để tránh cản trở hoạt động săn lùng của chúng tôi. Vậy nên tao sẽ phải yêu cầu cậu...</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Rồi thì tụi ta được một nhóm Outcasts gần đó nhận nuôi, ai ngờ hóa ra toàn bộ chỉ là bẫy.</t>
+          <t>Rồi thì tụi tao được một nhóm Outcasts gần đó nhận nuôi, ai ngờ hóa ra toàn bộ chỉ là bẫy.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Ta biết ngươi có thù oán với Roya và Spacetrek Collective, nhưng chắc chắn ngươi có thể tin họ hơn đám Outcasts kia.</t>
+          <t>Tao biết mày có thù oán với Roya và Spacetrek Collective, nhưng chắc chắn mày có thể tin họ hơn đám Outcasts kia.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Tin ta đi, Tập đoàn Spacetrek đáng tin cậy hơn đám Outcasts kia nhiều.</t>
+          <t>Tin tao đi, Tập đoàn Spacetrek đáng tin cậy hơn đám Outcasts kia nhiều.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Cậu đang làm gì đấy?! Tránh xa mấy thùng hàng đó ra!</t>
+          <t>Mày đang làm gì đấy?! Tránh xa mấy thùng hàng đó ra!</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Ta muốn cậu ngăn bọn Outcast lợi dụng chúng ta và hệ sinh thái của chúng ta. Một khi làm được điều đó, cậu có thể lấy bất kỳ vật tư nào từ trại của chúng.</t>
+          <t>Tao muốn cậu ngăn bọn Outcast lợi dụng chúng ta và hệ sinh thái của chúng ta. Một khi làm được điều đó, cậu có thể lấy bất kỳ vật tư nào từ trại của chúng.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Ta nghe thấy giọng nói của ai đó từ rất lâu rồi.</t>
+          <t>Tao nghe thấy giọng nói của ai đó từ rất lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Ý cậu là thế hả!? Thô lỗ quá!</t>
+          <t>Ý mày là thế hả!? Thô lỗ quá!</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>"Được rồi, thế thì... ta cần tìm cách trở nên mạnh mẽ hơn. Khi trở về Bjartr Woods, ta sẽ tìm kiếm sự chỉ dẫn từ Giant Soliskin!"</t>
+          <t>"Được rồi, thế thì... tao cần tìm cách trở nên mạnh mẽ hơn. Khi trở về Bjartr Woods, tao sẽ tìm kiếm sự chỉ dẫn từ Giant Soliskin!"</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Ta sẽ đi xem sao.</t>
+          <t>Tao sẽ đi xem sao.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Ơ, cậu từ đâu chui ra thế?!</t>
+          <t>Ơ, mày từ đâu chui ra thế?!</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Này! Đây là lần thứ hai rồi đấy!!! Lần trước cậu bảo đã chừa rồi cơ mà!</t>
+          <t>Này! Đây là lần thứ hai rồi đấy!!! Lần trước mày bảo đã chừa rồi cơ mà!</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Thì ta bám theo ngươi để khỏi lạc nhau thôi...</t>
+          <t>Thì tao bám theo mày để khỏi lạc nhau thôi...</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Cậu định đi đâu vậy?</t>
+          <t>Mày định đi đâu vậy?</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Trời ạ! Ta phải hoãn cả dự án của mình chỉ để đi theo ngươi đến đây!</t>
+          <t>Trời ạ! Tao phải hoãn cả dự án của mình chỉ để đi theo mày đến đây!</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Soliskin trốn trong này. Ta không ngờ chúng lại sống trong hang!</t>
+          <t>Soliskin trốn trong này. Tao không ngờ chúng lại sống trong hang!</t>
         </is>
       </c>
     </row>
